--- a/output/StructureDefinition-RNDSRegistroEletronicoDispensacaoFornecimentoMedicamentos.xlsx
+++ b/output/StructureDefinition-RNDSRegistroEletronicoDispensacaoFornecimentoMedicamentos.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8609" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8615" uniqueCount="806">
   <si>
     <t>Property</t>
   </si>
@@ -1860,10 +1860,16 @@
     <t>Composition.section:dispensedMedications.title</t>
   </si>
   <si>
+    <t>Label for section (e.g. for ToC)</t>
+  </si>
+  <si>
     <t>Medicamentos Dispensados</t>
   </si>
   <si>
     <t>Composition.section:dispensedMedications.code</t>
+  </si>
+  <si>
+    <t>Classification of section (recommended)</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1970,16 +1976,31 @@
     <t>Composition.section:dispensedMedications.author</t>
   </si>
   <si>
+    <t>Who and/or what authored the section</t>
+  </si>
+  <si>
     <t>Composition.section:dispensedMedications.focus</t>
   </si>
   <si>
+    <t>Who/what the section is about, when it is not about the subject of composition</t>
+  </si>
+  <si>
     <t>Composition.section:dispensedMedications.text</t>
   </si>
   <si>
+    <t>Text summary of the section, for human interpretation</t>
+  </si>
+  <si>
     <t>Composition.section:dispensedMedications.mode</t>
   </si>
   <si>
+    <t>working | snapshot | changes</t>
+  </si>
+  <si>
     <t>Composition.section:dispensedMedications.orderedBy</t>
+  </si>
+  <si>
+    <t>Order of section entries</t>
   </si>
   <si>
     <t>Composition.section:dispensedMedications.entry</t>
@@ -1989,6 +2010,9 @@
 </t>
   </si>
   <si>
+    <t>A reference to data that supports this section</t>
+  </si>
+  <si>
     <t>Composition.section:dispensedMedications.entry.id</t>
   </si>
   <si>
@@ -2028,7 +2052,13 @@
     <t>Composition.section:dispensedMedications.emptyReason</t>
   </si>
   <si>
+    <t>Why the section is empty</t>
+  </si>
+  <si>
     <t>Composition.section:dispensedMedications.section</t>
+  </si>
+  <si>
+    <t>Nested Section</t>
   </si>
   <si>
     <t>Composition.section:prescriptionInformation</t>
@@ -2147,88 +2177,58 @@
     <t>Composition.section.section.title</t>
   </si>
   <si>
-    <t>Label for section (e.g. for ToC)</t>
-  </si>
-  <si>
     <t>Composition.section:prescriptionInformation.section.code</t>
   </si>
   <si>
     <t>Composition.section.section.code</t>
   </si>
   <si>
-    <t>Classification of section (recommended)</t>
-  </si>
-  <si>
     <t>Composition.section:prescriptionInformation.section.author</t>
   </si>
   <si>
     <t>Composition.section.section.author</t>
   </si>
   <si>
-    <t>Who and/or what authored the section</t>
-  </si>
-  <si>
     <t>Composition.section:prescriptionInformation.section.focus</t>
   </si>
   <si>
     <t>Composition.section.section.focus</t>
   </si>
   <si>
-    <t>Who/what the section is about, when it is not about the subject of composition</t>
-  </si>
-  <si>
     <t>Composition.section:prescriptionInformation.section.text</t>
   </si>
   <si>
     <t>Composition.section.section.text</t>
   </si>
   <si>
-    <t>Text summary of the section, for human interpretation</t>
-  </si>
-  <si>
     <t>Composition.section:prescriptionInformation.section.mode</t>
   </si>
   <si>
     <t>Composition.section.section.mode</t>
   </si>
   <si>
-    <t>working | snapshot | changes</t>
-  </si>
-  <si>
     <t>Composition.section:prescriptionInformation.section.orderedBy</t>
   </si>
   <si>
     <t>Composition.section.section.orderedBy</t>
   </si>
   <si>
-    <t>Order of section entries</t>
-  </si>
-  <si>
     <t>Composition.section:prescriptionInformation.section.entry</t>
   </si>
   <si>
     <t>Composition.section.section.entry</t>
   </si>
   <si>
-    <t>A reference to data that supports this section</t>
-  </si>
-  <si>
     <t>Composition.section:prescriptionInformation.section.emptyReason</t>
   </si>
   <si>
     <t>Composition.section.section.emptyReason</t>
   </si>
   <si>
-    <t>Why the section is empty</t>
-  </si>
-  <si>
     <t>Composition.section:prescriptionInformation.section.section</t>
   </si>
   <si>
     <t>Composition.section.section.section</t>
-  </si>
-  <si>
-    <t>Nested Section</t>
   </si>
   <si>
     <t>Composition.section:prescriptionInformation.section:prescriptionReason</t>
@@ -14717,7 +14717,7 @@
         <v>183</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>524</v>
+        <v>287</v>
       </c>
       <c r="M102" t="s" s="2">
         <v>185</v>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14832,12 +14832,14 @@
         <v>137</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14904,7 +14906,7 @@
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14925,7 +14927,7 @@
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>78</v>
+        <v>417</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14947,13 +14949,17 @@
         <v>137</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>499</v>
+        <v>418</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
       </c>
@@ -15019,7 +15025,7 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -15062,7 +15068,7 @@
         <v>183</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>529</v>
+        <v>598</v>
       </c>
       <c r="M105" t="s" s="2">
         <v>530</v>
@@ -15078,7 +15084,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>78</v>
@@ -15152,7 +15158,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>533</v>
@@ -15181,7 +15187,7 @@
         <v>171</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>534</v>
+        <v>601</v>
       </c>
       <c r="M106" t="s" s="2">
         <v>535</v>
@@ -15200,7 +15206,7 @@
         <v>78</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>78</v>
@@ -15219,7 +15225,7 @@
       </c>
       <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>78</v>
@@ -15269,10 +15275,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15384,10 +15390,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15501,10 +15507,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15530,7 +15536,7 @@
         <v>194</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="M109" t="s" s="2">
         <v>196</v>
@@ -15620,10 +15626,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15735,10 +15741,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15852,10 +15858,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15881,7 +15887,7 @@
         <v>105</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="M112" t="s" s="2">
         <v>205</v>
@@ -15971,10 +15977,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16000,7 +16006,7 @@
         <v>183</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M113" t="s" s="2">
         <v>212</v>
@@ -16088,10 +16094,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16117,7 +16123,7 @@
         <v>111</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="M114" t="s" s="2">
         <v>218</v>
@@ -16131,7 +16137,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>78</v>
@@ -16205,10 +16211,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16234,7 +16240,7 @@
         <v>183</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M115" t="s" s="2">
         <v>223</v>
@@ -16322,10 +16328,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16351,7 +16357,7 @@
         <v>228</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>230</v>
@@ -16441,10 +16447,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16470,7 +16476,7 @@
         <v>183</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="M117" t="s" s="2">
         <v>237</v>
@@ -16560,7 +16566,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>540</v>
@@ -16589,7 +16595,7 @@
         <v>541</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>542</v>
+        <v>635</v>
       </c>
       <c r="M118" t="s" s="2">
         <v>543</v>
@@ -16677,7 +16683,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>544</v>
@@ -16706,7 +16712,7 @@
         <v>512</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>545</v>
+        <v>637</v>
       </c>
       <c r="M119" t="s" s="2">
         <v>546</v>
@@ -16794,7 +16800,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>549</v>
@@ -16823,7 +16829,7 @@
         <v>121</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>550</v>
+        <v>639</v>
       </c>
       <c r="M120" t="s" s="2">
         <v>551</v>
@@ -16911,7 +16917,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>555</v>
@@ -16940,7 +16946,7 @@
         <v>111</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>556</v>
+        <v>641</v>
       </c>
       <c r="M121" t="s" s="2">
         <v>557</v>
@@ -17030,7 +17036,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>563</v>
@@ -17059,7 +17065,7 @@
         <v>171</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>564</v>
+        <v>643</v>
       </c>
       <c r="M122" t="s" s="2">
         <v>565</v>
@@ -17149,7 +17155,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>571</v>
@@ -17175,10 +17181,10 @@
         <v>78</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>572</v>
+        <v>646</v>
       </c>
       <c r="M123" t="s" s="2">
         <v>573</v>
@@ -17266,10 +17272,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17381,10 +17387,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17498,10 +17504,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17615,10 +17621,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17732,10 +17738,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17849,10 +17855,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17966,7 +17972,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>578</v>
@@ -17995,7 +18001,7 @@
         <v>171</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>579</v>
+        <v>660</v>
       </c>
       <c r="M130" t="s" s="2">
         <v>580</v>
@@ -18083,9 +18089,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>586</v>
@@ -18102,7 +18108,7 @@
         <v>80</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>78</v>
@@ -18114,7 +18120,7 @@
         <v>81</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>587</v>
+        <v>662</v>
       </c>
       <c r="M131" t="s" s="2">
         <v>588</v>
@@ -18202,13 +18208,13 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>653</v>
+        <v>663</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>516</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>654</v>
+        <v>664</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>78</v>
@@ -18319,7 +18325,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>523</v>
@@ -18348,7 +18354,7 @@
         <v>183</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>524</v>
+        <v>287</v>
       </c>
       <c r="M133" t="s" s="2">
         <v>185</v>
@@ -18434,14 +18440,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>656</v>
+        <v>666</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>525</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -18463,12 +18469,14 @@
         <v>137</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N134" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -18535,7 +18543,7 @@
         <v>78</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>78</v>
@@ -18549,14 +18557,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>526</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>78</v>
+        <v>417</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18578,13 +18586,17 @@
         <v>137</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>499</v>
+        <v>418</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O135" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="P135" t="s" s="2">
         <v>78</v>
       </c>
@@ -18650,7 +18662,7 @@
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>78</v>
@@ -18664,7 +18676,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>658</v>
+        <v>668</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>527</v>
@@ -18693,7 +18705,7 @@
         <v>183</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>529</v>
+        <v>598</v>
       </c>
       <c r="M136" t="s" s="2">
         <v>530</v>
@@ -18709,7 +18721,7 @@
       </c>
       <c r="Q136" s="2"/>
       <c r="R136" t="s" s="2">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="S136" t="s" s="2">
         <v>78</v>
@@ -18783,7 +18795,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>533</v>
@@ -18812,7 +18824,7 @@
         <v>171</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>534</v>
+        <v>601</v>
       </c>
       <c r="M137" t="s" s="2">
         <v>535</v>
@@ -18831,7 +18843,7 @@
         <v>78</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>78</v>
@@ -18850,7 +18862,7 @@
       </c>
       <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>78</v>
@@ -18900,10 +18912,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19015,10 +19027,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19132,10 +19144,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>664</v>
+        <v>674</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19161,7 +19173,7 @@
         <v>194</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="M140" t="s" s="2">
         <v>196</v>
@@ -19251,10 +19263,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19366,10 +19378,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19483,10 +19495,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19512,7 +19524,7 @@
         <v>105</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="M143" t="s" s="2">
         <v>205</v>
@@ -19602,10 +19614,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19631,7 +19643,7 @@
         <v>183</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M144" t="s" s="2">
         <v>212</v>
@@ -19719,10 +19731,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19748,7 +19760,7 @@
         <v>111</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="M145" t="s" s="2">
         <v>218</v>
@@ -19762,7 +19774,7 @@
       </c>
       <c r="Q145" s="2"/>
       <c r="R145" t="s" s="2">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="S145" t="s" s="2">
         <v>78</v>
@@ -19836,10 +19848,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19865,7 +19877,7 @@
         <v>183</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M146" t="s" s="2">
         <v>223</v>
@@ -19953,10 +19965,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19982,7 +19994,7 @@
         <v>228</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M147" t="s" s="2">
         <v>230</v>
@@ -20072,10 +20084,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20101,7 +20113,7 @@
         <v>183</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="M148" t="s" s="2">
         <v>237</v>
@@ -20191,7 +20203,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>540</v>
@@ -20220,7 +20232,7 @@
         <v>541</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>542</v>
+        <v>635</v>
       </c>
       <c r="M149" t="s" s="2">
         <v>543</v>
@@ -20308,7 +20320,7 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>544</v>
@@ -20337,7 +20349,7 @@
         <v>512</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>545</v>
+        <v>637</v>
       </c>
       <c r="M150" t="s" s="2">
         <v>546</v>
@@ -20425,7 +20437,7 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>549</v>
@@ -20454,7 +20466,7 @@
         <v>121</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>550</v>
+        <v>639</v>
       </c>
       <c r="M151" t="s" s="2">
         <v>551</v>
@@ -20542,7 +20554,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>555</v>
@@ -20571,7 +20583,7 @@
         <v>111</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>556</v>
+        <v>641</v>
       </c>
       <c r="M152" t="s" s="2">
         <v>557</v>
@@ -20661,7 +20673,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>678</v>
+        <v>688</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>563</v>
@@ -20690,7 +20702,7 @@
         <v>171</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>564</v>
+        <v>643</v>
       </c>
       <c r="M153" t="s" s="2">
         <v>565</v>
@@ -20780,7 +20792,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>571</v>
@@ -20809,7 +20821,7 @@
         <v>512</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>572</v>
+        <v>646</v>
       </c>
       <c r="M154" t="s" s="2">
         <v>573</v>
@@ -20897,7 +20909,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>578</v>
@@ -20926,7 +20938,7 @@
         <v>171</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>579</v>
+        <v>660</v>
       </c>
       <c r="M155" t="s" s="2">
         <v>580</v>
@@ -21016,7 +21028,7 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>681</v>
+        <v>691</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>586</v>
@@ -21045,7 +21057,7 @@
         <v>81</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>587</v>
+        <v>662</v>
       </c>
       <c r="M156" t="s" s="2">
         <v>588</v>
@@ -21131,10 +21143,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>683</v>
+        <v>693</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21246,10 +21258,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21363,10 +21375,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21482,10 +21494,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>688</v>
+        <v>698</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21511,7 +21523,7 @@
         <v>183</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>690</v>
+        <v>598</v>
       </c>
       <c r="M160" t="s" s="2">
         <v>530</v>
@@ -21601,10 +21613,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21630,7 +21642,7 @@
         <v>171</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>693</v>
+        <v>601</v>
       </c>
       <c r="M161" t="s" s="2">
         <v>535</v>
@@ -21720,10 +21732,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21749,7 +21761,7 @@
         <v>541</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>696</v>
+        <v>635</v>
       </c>
       <c r="M162" t="s" s="2">
         <v>543</v>
@@ -21837,10 +21849,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21866,7 +21878,7 @@
         <v>512</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>699</v>
+        <v>637</v>
       </c>
       <c r="M163" t="s" s="2">
         <v>546</v>
@@ -21954,10 +21966,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21983,7 +21995,7 @@
         <v>121</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>702</v>
+        <v>639</v>
       </c>
       <c r="M164" t="s" s="2">
         <v>551</v>
@@ -22071,10 +22083,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22100,7 +22112,7 @@
         <v>111</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>705</v>
+        <v>641</v>
       </c>
       <c r="M165" t="s" s="2">
         <v>557</v>
@@ -22190,10 +22202,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22219,7 +22231,7 @@
         <v>171</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>708</v>
+        <v>643</v>
       </c>
       <c r="M166" t="s" s="2">
         <v>565</v>
@@ -22309,10 +22321,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22338,7 +22350,7 @@
         <v>512</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>711</v>
+        <v>646</v>
       </c>
       <c r="M167" t="s" s="2">
         <v>573</v>
@@ -22426,10 +22438,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22455,7 +22467,7 @@
         <v>171</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>714</v>
+        <v>660</v>
       </c>
       <c r="M168" t="s" s="2">
         <v>580</v>
@@ -22545,10 +22557,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22574,7 +22586,7 @@
         <v>78</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>717</v>
+        <v>662</v>
       </c>
       <c r="M169" t="s" s="2">
         <v>588</v>
@@ -22693,7 +22705,7 @@
         <v>406</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>717</v>
+        <v>662</v>
       </c>
       <c r="M170" t="s" s="2">
         <v>588</v>
@@ -22784,7 +22796,7 @@
         <v>720</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>683</v>
+        <v>693</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22899,7 +22911,7 @@
         <v>721</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23016,7 +23028,7 @@
         <v>722</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23135,7 +23147,7 @@
         <v>723</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23161,7 +23173,7 @@
         <v>183</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>690</v>
+        <v>598</v>
       </c>
       <c r="M174" t="s" s="2">
         <v>530</v>
@@ -23254,7 +23266,7 @@
         <v>725</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23280,7 +23292,7 @@
         <v>171</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>693</v>
+        <v>601</v>
       </c>
       <c r="M175" t="s" s="2">
         <v>535</v>
@@ -23629,7 +23641,7 @@
         <v>194</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="M178" t="s" s="2">
         <v>196</v>
@@ -23980,7 +23992,7 @@
         <v>105</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="M181" t="s" s="2">
         <v>205</v>
@@ -24099,7 +24111,7 @@
         <v>183</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M182" t="s" s="2">
         <v>212</v>
@@ -24216,7 +24228,7 @@
         <v>111</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="M183" t="s" s="2">
         <v>218</v>
@@ -24333,7 +24345,7 @@
         <v>183</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M184" t="s" s="2">
         <v>223</v>
@@ -24450,7 +24462,7 @@
         <v>228</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M185" t="s" s="2">
         <v>230</v>
@@ -24569,7 +24581,7 @@
         <v>183</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="M186" t="s" s="2">
         <v>237</v>
@@ -24662,7 +24674,7 @@
         <v>751</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24688,7 +24700,7 @@
         <v>541</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>696</v>
+        <v>635</v>
       </c>
       <c r="M187" t="s" s="2">
         <v>543</v>
@@ -24779,7 +24791,7 @@
         <v>752</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24805,7 +24817,7 @@
         <v>512</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>699</v>
+        <v>637</v>
       </c>
       <c r="M188" t="s" s="2">
         <v>546</v>
@@ -24896,7 +24908,7 @@
         <v>753</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24922,7 +24934,7 @@
         <v>121</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>702</v>
+        <v>639</v>
       </c>
       <c r="M189" t="s" s="2">
         <v>551</v>
@@ -25013,7 +25025,7 @@
         <v>754</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25039,7 +25051,7 @@
         <v>111</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>705</v>
+        <v>641</v>
       </c>
       <c r="M190" t="s" s="2">
         <v>557</v>
@@ -25132,7 +25144,7 @@
         <v>755</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25158,7 +25170,7 @@
         <v>171</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>708</v>
+        <v>643</v>
       </c>
       <c r="M191" t="s" s="2">
         <v>565</v>
@@ -25251,7 +25263,7 @@
         <v>756</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25277,7 +25289,7 @@
         <v>757</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>711</v>
+        <v>646</v>
       </c>
       <c r="M192" t="s" s="2">
         <v>573</v>
@@ -26068,7 +26080,7 @@
         <v>770</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26094,7 +26106,7 @@
         <v>171</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>714</v>
+        <v>660</v>
       </c>
       <c r="M199" t="s" s="2">
         <v>580</v>
@@ -26187,7 +26199,7 @@
         <v>771</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26213,7 +26225,7 @@
         <v>81</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>717</v>
+        <v>662</v>
       </c>
       <c r="M200" t="s" s="2">
         <v>588</v>
@@ -26332,7 +26344,7 @@
         <v>406</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>717</v>
+        <v>662</v>
       </c>
       <c r="M201" t="s" s="2">
         <v>588</v>
@@ -26423,7 +26435,7 @@
         <v>774</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>683</v>
+        <v>693</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26538,7 +26550,7 @@
         <v>775</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -26655,7 +26667,7 @@
         <v>776</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -26774,7 +26786,7 @@
         <v>777</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -26800,7 +26812,7 @@
         <v>183</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>690</v>
+        <v>598</v>
       </c>
       <c r="M205" t="s" s="2">
         <v>530</v>
@@ -26893,7 +26905,7 @@
         <v>779</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -26919,7 +26931,7 @@
         <v>171</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>693</v>
+        <v>601</v>
       </c>
       <c r="M206" t="s" s="2">
         <v>535</v>
@@ -26938,7 +26950,7 @@
         <v>78</v>
       </c>
       <c r="S206" t="s" s="2">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="T206" t="s" s="2">
         <v>78</v>
@@ -27268,7 +27280,7 @@
         <v>194</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="M209" t="s" s="2">
         <v>196</v>
@@ -27619,7 +27631,7 @@
         <v>105</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="M212" t="s" s="2">
         <v>205</v>
@@ -27738,7 +27750,7 @@
         <v>183</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M213" t="s" s="2">
         <v>212</v>
@@ -27855,7 +27867,7 @@
         <v>111</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="M214" t="s" s="2">
         <v>218</v>
@@ -27869,7 +27881,7 @@
       </c>
       <c r="Q214" s="2"/>
       <c r="R214" t="s" s="2">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="S214" t="s" s="2">
         <v>78</v>
@@ -27972,7 +27984,7 @@
         <v>183</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M215" t="s" s="2">
         <v>223</v>
@@ -28089,7 +28101,7 @@
         <v>228</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M216" t="s" s="2">
         <v>230</v>
@@ -28208,7 +28220,7 @@
         <v>183</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="M217" t="s" s="2">
         <v>237</v>
@@ -28301,7 +28313,7 @@
         <v>791</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28327,7 +28339,7 @@
         <v>541</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>696</v>
+        <v>635</v>
       </c>
       <c r="M218" t="s" s="2">
         <v>543</v>
@@ -28418,7 +28430,7 @@
         <v>792</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -28444,7 +28456,7 @@
         <v>512</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>699</v>
+        <v>637</v>
       </c>
       <c r="M219" t="s" s="2">
         <v>546</v>
@@ -28535,7 +28547,7 @@
         <v>793</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -28561,7 +28573,7 @@
         <v>121</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>702</v>
+        <v>639</v>
       </c>
       <c r="M220" t="s" s="2">
         <v>551</v>
@@ -28652,7 +28664,7 @@
         <v>794</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -28678,7 +28690,7 @@
         <v>111</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>705</v>
+        <v>641</v>
       </c>
       <c r="M221" t="s" s="2">
         <v>557</v>
@@ -28771,7 +28783,7 @@
         <v>795</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -28797,7 +28809,7 @@
         <v>171</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>708</v>
+        <v>643</v>
       </c>
       <c r="M222" t="s" s="2">
         <v>565</v>
@@ -28890,7 +28902,7 @@
         <v>796</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -28916,7 +28928,7 @@
         <v>797</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>711</v>
+        <v>646</v>
       </c>
       <c r="M223" t="s" s="2">
         <v>573</v>
@@ -29707,7 +29719,7 @@
         <v>804</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -29733,7 +29745,7 @@
         <v>171</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>714</v>
+        <v>660</v>
       </c>
       <c r="M230" t="s" s="2">
         <v>580</v>
@@ -29826,7 +29838,7 @@
         <v>805</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -29852,7 +29864,7 @@
         <v>81</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>717</v>
+        <v>662</v>
       </c>
       <c r="M231" t="s" s="2">
         <v>588</v>
